--- a/حركات_الشركات_منظمة/البصريات/حركات_VISN.xlsx
+++ b/حركات_الشركات_منظمة/البصريات/حركات_VISN.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34653B40-A975-424E-9E3F-FE62365F0B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="النظارات" state="visible" r:id="rId4"/>
+    <sheet name="النظارات" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="54">
   <si>
     <t>اسم المريض</t>
   </si>
@@ -97,7 +101,7 @@
     <t>VISN005</t>
   </si>
   <si>
-    <t xml:space="preserve"> 27/4/2026</t>
+    <t> 27/4/2026</t>
   </si>
   <si>
     <t xml:space="preserve">انس يوسف مفتاح صدقي </t>
@@ -109,10 +113,10 @@
     <t>VISN006</t>
   </si>
   <si>
-    <t xml:space="preserve"> 500</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> سامي احمد شوقي سوده بك زاده</t>
+    <t> 500</t>
+  </si>
+  <si>
+    <t> سامي احمد شوقي سوده بك زاده</t>
   </si>
   <si>
     <t>VISN20250007W1</t>
@@ -173,35 +177,31 @@
   </si>
   <si>
     <t>18/6/2026</t>
-  </si>
-  <si>
-    <t>VISN2025</t>
-  </si>
-  <si>
-    <t>VISN00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -572,9 +572,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.69921875" customWidth="1"/>
     <col min="2" max="2" width="35.09765625" customWidth="1"/>
@@ -586,7 +586,7 @@
     <col min="10" max="10" width="19.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -606,7 +606,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -626,7 +626,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -646,7 +646,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -666,7 +666,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -686,7 +686,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -706,7 +706,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -726,7 +726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -769,7 +769,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -789,7 +789,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -809,7 +809,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -829,7 +829,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>50</v>
       </c>
@@ -849,80 +849,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>